--- a/max_spotify.xlsx
+++ b/max_spotify.xlsx
@@ -606,31 +606,31 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>duration_ms</t>
+          <t>track_album_release_date_year</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>517810</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>track_album_release_date_year</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2020</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>duration_minutes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="21">

--- a/max_spotify.xlsx
+++ b/max_spotify.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,8 +529,10 @@
           <t>loudness</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1.275</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -616,30 +618,40 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>loudness_shifted</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>61.275</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.630000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>playlist_genre_count_per_song</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>10</v>
       </c>
     </row>

--- a/max_spotify.xlsx
+++ b/max_spotify.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,10 +529,8 @@
           <t>loudness</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B10" t="n">
+        <v>0.8219800524029137</v>
       </c>
     </row>
     <row r="11">
@@ -618,40 +616,30 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>loudness_shifted</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61.275</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>duration_minutes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_genre_count_per_song</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.630000000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>playlist_genre_count_per_song</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
         <v>10</v>
       </c>
     </row>

--- a/max_spotify.xlsx
+++ b/max_spotify.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,40 +606,52 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>track_album_release_date_year</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2020</v>
+          <t>track_album_release_date_converted</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>track_album_release_date_year</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.630000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>playlist_genre_count_per_song</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>10</v>
       </c>
     </row>
